--- a/测试集/泛用性验收_v3/W3/W3_预期_全年更新.xlsx
+++ b/测试集/泛用性验收_v3/W3/W3_预期_全年更新.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -42,16 +52,86 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -413,109 +493,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>责任单位</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>完成时限</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>计划数</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>完成数</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>完成率</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>任务1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>单位0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <f>F2/E2</f>
-        <v/>
-      </c>
+      <c r="H2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>任务2</t>
+          <t>完成年度预算编制</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>单位1</t>
+          <t>综合办公室</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <f>F3/E3</f>
@@ -525,29 +591,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>任务3</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>单位2</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <f>F4/E4</f>
@@ -557,29 +623,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>任务4</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>单位3</t>
+          <t>工程技术部</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <f>F5/E5</f>
@@ -589,29 +655,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>任务5</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>单位0</t>
+          <t>安全管理部</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <f>F6/E6</f>
@@ -621,29 +687,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>任务6</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>单位1</t>
+          <t>综合办公室</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G7">
         <f>F7/E7</f>
@@ -653,29 +719,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A007</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>任务7</t>
+          <t>成本合计核算</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>单位2</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <f>F8/E8</f>
@@ -685,36 +751,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A008</t>
+          <t>A007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>任务8</t>
+          <t>供应商评估审查</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>单位3</t>
+          <t>工程技术部</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <f>F9/E9</f>
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A008</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>新员工入职办理</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10">
+        <f>F10/E10</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G3:G10">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/测试集/泛用性验收_v3/W3/W3_预期_全年更新.xlsx
+++ b/测试集/泛用性验收_v3/W3/W3_预期_全年更新.xlsx
@@ -116,7 +116,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -493,159 +495,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>任务执行情况统计表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>填报说明：请各单位如实填报执行进度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>基本信息</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>进度</t>
         </is>
       </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr"/>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>责任单位</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>完成时限</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>计划数</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>完成数</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>完成率</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>完成年度预算编制</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>综合办公室</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <f>F3/E3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>组织安全培训演练</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <f>F4/E4</f>
-        <v/>
-      </c>
+      <c r="H4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>完成年度预算编制</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>工程技术部</t>
+          <t>综合办公室</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <f>F5/E5</f>
@@ -655,29 +607,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>安全管理部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <f>F6/E6</f>
@@ -687,29 +639,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>完成资料汇总</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>综合办公室</t>
+          <t>工程技术部</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <f>F7/E7</f>
@@ -719,29 +671,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>成本合计核算</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>安全管理部</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G8">
         <f>F8/E8</f>
@@ -751,29 +703,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A007</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>供应商评估审查</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>工程技术部</t>
+          <t>综合办公室</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="G9">
         <f>F9/E9</f>
@@ -783,41 +735,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A008</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新员工入职办理</t>
+          <t>成本合计核算</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>安全管理部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <f>F10/E10</f>
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>供应商评估审查</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>工程技术部</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <f>F11/E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A008</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>新员工入职办理</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>安全管理部</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <f>F12/E12</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:G1"/>
+  <mergeCells count="4">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G10">
+  <conditionalFormatting sqref="G5:G12">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.5</formula>
     </cfRule>
